--- a/pensum/ok10/LOM_Ovingsark_Okonomistyring_kap10_Investering_NY.xlsx
+++ b/pensum/ok10/LOM_Ovingsark_Okonomistyring_kap10_Investering_NY.xlsx
@@ -322,7 +322,7 @@
     <t xml:space="preserve">Bransjetall: NHO Elektro, Lønnsomhetsrapport 2025, gjengitt i Elektro 24-7 19.08.2026 (hentet 10.09.2026). De 809 er bedriftene i datagrunnlaget, ikke bransjen. NHO Elektro oppgir ikke svarprosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Bok 1.</t>
+    <t xml:space="preserve">Nordlys Elektro AS er en konstruert casebedrift. Tallene henger sammen på tvers av alle ti kapitlene i Økonomistyring for LØM-emnet.</t>
   </si>
   <si>
     <t xml:space="preserve">Lønner investeringen seg?</t>
@@ -535,7 +535,7 @@
     <t xml:space="preserve">Prøv dette: sett avkastningskravet i B12 til 16 %. Nåverdien snur, uten at ett eneste tall om utstyret er rørt. Det er hele beslutningsregelen i én celle.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 10.1 til 10.3. Tallene er investeringen Nordlys Elektro AS vurderer i 2027.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 10.1 til 10.3. Tallene er investeringen Nordlys Elektro AS vurderer i 2027.</t>
   </si>
   <si>
     <t xml:space="preserve">Nåverdien ved ulike avkastningskrav</t>
@@ -604,7 +604,7 @@
     <t xml:space="preserve">Stemmer raden for dagens krav med kalkulatoren?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 10.2 og 10.3.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 10.2 og 10.3.</t>
   </si>
   <si>
     <t xml:space="preserve">To investeringer til samme pris</t>
@@ -709,7 +709,7 @@
     <t xml:space="preserve">Prøv dette: skru avkastningskravet i Investering!B12 oppover. Ved hvilket krav slutter A å være lønnsom, og ved hvilket krav slutter B? Forskjellen mellom de to tallene er hvor mye mer B tåler før den ryker.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 10.1 til 10.3, og avsnittet om hva tilbakebetalingsmetoden ikke ser. Prisen er den samme som utstyret i kapitlets hovedeksempel.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 10.1 til 10.3, og avsnittet om hva tilbakebetalingsmetoden ikke ser. Prisen er den samme som utstyret i kapitlets hovedeksempel.</t>
   </si>
   <si>
     <t xml:space="preserve">Linja som skal i kabel</t>
@@ -787,7 +787,7 @@
     <t xml:space="preserve">Er levetiden lengre enn nullpunktet i år?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Bok 1 kap. 10.1 og 10.2. Fjellkraft Nett AS er nettselskapet Nordlys Elektro AS har rammeavtale med. Tallene er didaktiske forutsetninger, oppgitt i oppgaven slik eksamensoppgaver gjør det.</t>
+    <t xml:space="preserve">Kilde: Økonomistyring for LØM-emnet kap. 10.1 og 10.2. Fjellkraft Nett AS er nettselskapet Nordlys Elektro AS har rammeavtale med. Tallene er didaktiske forutsetninger, oppgitt i oppgaven slik eksamensoppgaver gjør det.</t>
   </si>
   <si>
     <t xml:space="preserve">Din egen investering</t>
